--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_260_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_260_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1301</v>
+        <v>4.554</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8376</v>
+        <v>1.9254</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2925</v>
+        <v>2.6286</v>
       </c>
       <c r="G2" t="n">
         <v>0.828</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4323</v>
+        <v>-1.0084</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8653999999999999</v>
+        <v>-0.0468</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2977</v>
+        <v>-0.9616</v>
       </c>
       <c r="V2" t="n">
         <v>1.719</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9234</v>
+        <v>1.66</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0591</v>
+        <v>0.7009</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1357</v>
+        <v>0.959</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0396</v>
+        <v>0.8176</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9554</v>
+        <v>-0.3469</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0842</v>
+        <v>1.1644</v>
       </c>
       <c r="J3" t="n">
-        <v>2.393</v>
+        <v>0.925</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3562</v>
+        <v>0.3361</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0368</v>
+        <v>0.5889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6466</v>
+        <v>-0.1074</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4008</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0474</v>
+        <v>0.5756</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S3" t="n">
-        <v>0.188</v>
+        <v>-0.2478</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>-0.224</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6379</v>
+        <v>-0.0237</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5853</v>
+        <v>1.3502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6263</v>
+        <v>1.3514</v>
       </c>
       <c r="F4" t="n">
-        <v>0.959</v>
+        <v>-0.0012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8176</v>
+        <v>3.0396</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3469</v>
+        <v>1.9554</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1644</v>
+        <v>1.0842</v>
       </c>
       <c r="J4" t="n">
-        <v>0.925</v>
+        <v>2.393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3361</v>
+        <v>2.3562</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5889</v>
+        <v>0.0368</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1074</v>
+        <v>0.6466</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.4008</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5756</v>
+        <v>1.0474</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3224</v>
+        <v>-0.3853</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2987</v>
+        <v>0.1182</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0237</v>
+        <v>-0.5034</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4828</v>
+        <v>0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4583</v>
+        <v>0.8435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0245</v>
+        <v>-0.1436</v>
       </c>
       <c r="G5" t="n">
         <v>1.0903</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5353</v>
+        <v>-1.3181</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1202</v>
+        <v>-0.735</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4151</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. FERRARI</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1455</v>
+        <v>0.0139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0536</v>
+        <v>-2.2533</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1992</v>
+        <v>2.2672</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.168</v>
+        <v>2.8373</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1512</v>
+        <v>1.0673</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0167</v>
+        <v>1.77</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0536</v>
+        <v>2.0052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0168</v>
+        <v>1.7008</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>0.3044</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2216</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.168</v>
+        <v>-0.6335</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0535</v>
+        <v>1.4657</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0224</v>
+        <v>-1.5039</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.6917</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>-0.8123</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>F. FERRARI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2877</v>
+        <v>-0.1119</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7566</v>
+        <v>0.0536</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4688</v>
+        <v>-0.1656</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8373</v>
+        <v>-0.168</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0673</v>
+        <v>-0.1512</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>-0.0167</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0052</v>
+        <v>0.0536</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7008</v>
+        <v>0.0168</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3044</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8322000000000001</v>
+        <v>-0.2216</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6335</v>
+        <v>-0.168</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4657</v>
+        <v>-0.0535</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7834</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8055</v>
+        <v>0.056</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1949</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6106</v>
+        <v>0.056</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9162</v>
+        <v>-1.1521</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7873</v>
+        <v>1.5514</v>
       </c>
       <c r="F9" t="n">
         <v>-2.7035</v>
@@ -1156,10 +1156,10 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.224</v>
+        <v>-0.4599</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U9" t="n">
         <v>-0.2636</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.632</v>
+        <v>-2.9772</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0702</v>
+        <v>-3.4491</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4383</v>
+        <v>0.4719</v>
       </c>
       <c r="G10" t="n">
         <v>1.2377</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3208</v>
+        <v>-1.666</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5683</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7189</v>
       </c>
       <c r="V10" t="n">
         <v>0.9304</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2931</v>
+        <v>-4.0572</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.745</v>
+        <v>-3.5091</v>
       </c>
       <c r="F11" t="n">
         <v>-0.5481</v>
@@ -1312,10 +1312,10 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2502</v>
+        <v>-1.0143</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5780999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.7498</v>
+        <v>-7.1355</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7394</v>
+        <v>-6.957</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0104</v>
+        <v>-0.1785</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7476</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0897</v>
+        <v>-1.4754</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4936</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5961</v>
+        <v>-0.7641</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7454</v>
+        <v>-6.998499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.489</v>
+        <v>-9.7423</v>
       </c>
       <c r="F13" t="n">
         <v>2.7435</v>
@@ -1468,10 +1468,10 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.7698</v>
+        <v>-9.023100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.617</v>
+        <v>-3.870200000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-5.1529</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2484</v>
+        <v>6.31</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8957</v>
+        <v>3.9573</v>
       </c>
       <c r="F14" t="n">
         <v>2.3527</v>
@@ -1546,10 +1546,10 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7117</v>
+        <v>0.3499</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1202</v>
+        <v>-0.0587</v>
       </c>
       <c r="U14" t="n">
         <v>0.4086</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9555</v>
+        <v>2.9453</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9431</v>
+        <v>0.2354</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0124</v>
+        <v>2.7099</v>
       </c>
       <c r="G15" t="n">
         <v>2.0155</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4245</v>
+        <v>1.4143</v>
       </c>
       <c r="T15" t="n">
-        <v>1.628</v>
+        <v>0.9203</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7965</v>
+        <v>0.494</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2525</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9744</v>
+        <v>2.5944</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6338</v>
+        <v>0.2098</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3407</v>
+        <v>2.3846</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2522</v>
+        <v>0.3593</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5977</v>
+        <v>1.8619</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8499</v>
+        <v>-1.5026</v>
       </c>
       <c r="J16" t="n">
-        <v>0.341</v>
+        <v>1.1027</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6624</v>
+        <v>1.9697</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3213</v>
+        <v>-0.867</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5933</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1078</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5308</v>
+        <v>1.4851</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6122</v>
+        <v>0.4446</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9186</v>
+        <v>1.0405</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4251</v>
+        <v>2.0644</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.262</v>
+        <v>0.6902</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6871</v>
+        <v>1.3743</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3593</v>
+        <v>-0.2522</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8619</v>
+        <v>0.5977</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5026</v>
+        <v>-0.8499</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1027</v>
+        <v>0.341</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9697</v>
+        <v>0.6624</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.867</v>
+        <v>-0.3213</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.5933</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1078</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R17" t="n">
         <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3157</v>
+        <v>1.6208</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0272</v>
+        <v>0.6686</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3429</v>
+        <v>0.9522</v>
       </c>
       <c r="V17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6583</v>
+        <v>1.0857</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2796</v>
+        <v>1.8078</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6213</v>
+        <v>-0.7222</v>
       </c>
       <c r="G18" t="n">
         <v>0.3567</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7295</v>
+        <v>1.1569</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9752</v>
+        <v>0.5034</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7543</v>
+        <v>0.6535</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3558</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2033</v>
+        <v>0.1422</v>
       </c>
       <c r="E19" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.9686</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1236</v>
+        <v>1.1108</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6657</v>
+        <v>-1.8858</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7527</v>
+        <v>-0.4369</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0871</v>
+        <v>-1.4488</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3463</v>
+        <v>-1.378</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3095</v>
+        <v>0.1211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-1.4991</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.012</v>
+        <v>-0.5078</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0622</v>
+        <v>-0.5581</v>
       </c>
       <c r="O19" t="n">
         <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2839</v>
+        <v>0.7264</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0761</v>
+        <v>0.2675</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2078</v>
+        <v>0.4589</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1829</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.1829</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.3008</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.235</v>
+        <v>-1.8054</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3199</v>
+        <v>1.5046</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5558</v>
+        <v>-1.9815</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8837</v>
+        <v>-0.3253</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3279</v>
+        <v>-1.6562</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0163</v>
+        <v>-0.9448</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6554</v>
+        <v>0.4439</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6391</v>
+        <v>-1.3887</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5396</v>
+        <v>-1.0368</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2283</v>
+        <v>-0.7692</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3113</v>
+        <v>-0.2676</v>
       </c>
       <c r="P20" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5698</v>
+        <v>1.2169</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9085</v>
+        <v>0.5311</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3387</v>
+        <v>0.6858</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6664</v>
+        <v>-0.7915</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6764</v>
+        <v>-0.7068</v>
       </c>
       <c r="F21" t="n">
-        <v>1.01</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8858</v>
+        <v>0.5558</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4369</v>
+        <v>0.8837</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4488</v>
+        <v>-0.3279</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.378</v>
+        <v>0.0163</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1211</v>
+        <v>0.6554</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4991</v>
+        <v>-0.6391</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5078</v>
+        <v>0.5396</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5581</v>
+        <v>0.2283</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0502</v>
+        <v>0.3113</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.3332</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>0.4367</v>
       </c>
       <c r="U21" t="n">
-        <v>0.358</v>
+        <v>-0.1034</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>-2.1444</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2101</v>
+        <v>-0.9591</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5131</v>
+        <v>-0.9819</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3029</v>
+        <v>0.0228</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9815</v>
+        <v>-0.6657</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3253</v>
+        <v>-0.7527</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6562</v>
+        <v>0.0871</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9448</v>
+        <v>0.3463</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4439</v>
+        <v>0.3095</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3887</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0368</v>
+        <v>-1.012</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7692</v>
+        <v>-1.0622</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2676</v>
+        <v>0.0502</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3075</v>
+        <v>1.1215</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1766</v>
+        <v>1.0146</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4841</v>
+        <v>0.107</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-1.1829</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2881</v>
+        <v>-5.3451</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.889</v>
+        <v>-5.1813</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3991</v>
+        <v>-0.1639</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8914</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5979</v>
+        <v>0.3451</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2829</v>
+        <v>0.4248</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.315</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2284,16 +2284,16 @@
         <v>7.7455</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.743600000000001</v>
+        <v>-2.7435</v>
       </c>
       <c r="F24" t="n">
-        <v>10.4891</v>
+        <v>10.489</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1973</v>
       </c>
       <c r="H24" t="n">
-        <v>3.307199999999999</v>
+        <v>3.3072</v>
       </c>
       <c r="I24" t="n">
         <v>-5.5044</v>
@@ -2305,13 +2305,13 @@
         <v>7.476800000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.417899999999999</v>
+        <v>-4.4179</v>
       </c>
       <c r="M24" t="n">
         <v>-5.2562</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.169600000000001</v>
+        <v>-4.1696</v>
       </c>
       <c r="O24" t="n">
         <v>-1.0867</v>
@@ -2326,16 +2326,16 @@
         <v>16.2368</v>
       </c>
       <c r="S24" t="n">
-        <v>9.770000000000001</v>
+        <v>9.770099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>5.152900000000001</v>
+        <v>5.1529</v>
       </c>
       <c r="U24" t="n">
-        <v>4.617099999999999</v>
+        <v>4.6174</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1729000000000003</v>
+        <v>0.1728999999999998</v>
       </c>
       <c r="W24" t="n">
         <v>5.2814</v>
